--- a/output/yearly_benthic_cover_iteration_75_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_75_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.3625290946121</v>
+        <v>45.22471302949244</v>
       </c>
       <c r="M2" t="n">
-        <v>99.80918324839274</v>
+        <v>99.66822322223607</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.10501873937282</v>
+        <v>88.1176636498035</v>
       </c>
       <c r="C3" t="n">
-        <v>45.96287461885762</v>
+        <v>45.95744078166845</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228903888222476</v>
+        <v>2.22894039065265</v>
       </c>
       <c r="E3" t="n">
-        <v>5.730129896963143</v>
+        <v>5.727762075840063</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429679627408253</v>
+        <v>0.7429801302175502</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98417739867934</v>
+        <v>33.98214907382646</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17652628607796</v>
+        <v>34.1770859900073</v>
       </c>
       <c r="I3" t="n">
-        <v>6.598763539558911</v>
+        <v>6.615120175399799</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643549767130158</v>
+        <v>4.643625813859688</v>
       </c>
       <c r="K3" t="n">
-        <v>11.8949812606272</v>
+        <v>11.8823363501965</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90530076178889</v>
+        <v>48.92279632400165</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7631566412737</v>
+        <v>106.7625734558666</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.34776800020212</v>
+        <v>87.2728860755107</v>
       </c>
       <c r="C4" t="n">
-        <v>42.84542334348496</v>
+        <v>42.75582078727166</v>
       </c>
       <c r="D4" t="n">
-        <v>2.193265391852742</v>
+        <v>2.188650880996126</v>
       </c>
       <c r="E4" t="n">
-        <v>6.556931672612452</v>
+        <v>6.544934386449198</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445303571045142</v>
+        <v>0.7445477779234894</v>
       </c>
       <c r="G4" t="n">
-        <v>33.44079596834899</v>
+        <v>33.36790020068432</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24839642680765</v>
+        <v>34.2491977844805</v>
       </c>
       <c r="I4" t="n">
-        <v>5.510533451572565</v>
+        <v>5.524231432955242</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653314731903214</v>
+        <v>4.653423612021808</v>
       </c>
       <c r="K4" t="n">
-        <v>12.65223199979788</v>
+        <v>12.72711392448931</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31904566950721</v>
+        <v>44.33331195003348</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81670101279005</v>
+        <v>99.81624666179445</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.38535040661777</v>
+        <v>86.24831019926383</v>
       </c>
       <c r="C5" t="n">
-        <v>42.7384576646083</v>
+        <v>42.5887117354945</v>
       </c>
       <c r="D5" t="n">
-        <v>2.147039317342372</v>
+        <v>2.139194180216791</v>
       </c>
       <c r="E5" t="n">
-        <v>7.185445789345738</v>
+        <v>7.165661110157789</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458519682217868</v>
+        <v>0.7458748200664155</v>
       </c>
       <c r="G5" t="n">
-        <v>32.73598535497715</v>
+        <v>32.61388946731926</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30919053820219</v>
+        <v>34.3102417230551</v>
       </c>
       <c r="I5" t="n">
-        <v>4.600262637142368</v>
+        <v>4.611731273033387</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661574801386167</v>
+        <v>4.661717625415097</v>
       </c>
       <c r="K5" t="n">
-        <v>13.61464959338224</v>
+        <v>13.75168980073618</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49382236835467</v>
+        <v>43.50614759063168</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8469296263452</v>
+        <v>99.84654912686234</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.15792285921501</v>
+        <v>84.92993381455989</v>
       </c>
       <c r="C6" t="n">
-        <v>42.22582024875405</v>
+        <v>41.98676142542207</v>
       </c>
       <c r="D6" t="n">
-        <v>2.087527839357816</v>
+        <v>2.075044780819192</v>
       </c>
       <c r="E6" t="n">
-        <v>7.62616568780926</v>
+        <v>7.592265610411848</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469728501923151</v>
+        <v>0.747001556176634</v>
       </c>
       <c r="G6" t="n">
-        <v>31.82861171909658</v>
+        <v>31.63587567095779</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36075110884649</v>
+        <v>34.36207158412515</v>
       </c>
       <c r="I6" t="n">
-        <v>3.83931334021056</v>
+        <v>3.848914885965311</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668580313701969</v>
+        <v>4.668759726103962</v>
       </c>
       <c r="K6" t="n">
-        <v>14.842077140785</v>
+        <v>15.07006618544012</v>
       </c>
       <c r="L6" t="n">
-        <v>42.804317537207</v>
+        <v>42.81506874266469</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87221492674605</v>
+        <v>99.87189635352686</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.83658261834593</v>
+        <v>83.53268545275357</v>
       </c>
       <c r="C7" t="n">
-        <v>41.50117581950502</v>
+        <v>41.18751076849878</v>
       </c>
       <c r="D7" t="n">
-        <v>2.023703964949657</v>
+        <v>2.007417259228538</v>
       </c>
       <c r="E7" t="n">
-        <v>7.926921189158273</v>
+        <v>7.88008363576562</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479242764214578</v>
+        <v>0.7479588760690371</v>
       </c>
       <c r="G7" t="n">
-        <v>30.85548682052248</v>
+        <v>30.60483485451221</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40451671538706</v>
+        <v>34.40610829917569</v>
       </c>
       <c r="I7" t="n">
-        <v>3.203502924272878</v>
+        <v>3.211539552570981</v>
       </c>
       <c r="J7" t="n">
-        <v>4.67452672763411</v>
+        <v>4.674742975431482</v>
       </c>
       <c r="K7" t="n">
-        <v>16.16341738165409</v>
+        <v>16.46731454724643</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22875920605726</v>
+        <v>42.23826038186687</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89335240721637</v>
+        <v>99.89308569761208</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.85380057659812</v>
+        <v>88.37289581458106</v>
       </c>
       <c r="C8" t="n">
-        <v>43.89383783799826</v>
+        <v>43.48436559110929</v>
       </c>
       <c r="D8" t="n">
-        <v>2.028033913441431</v>
+        <v>2.011681886952134</v>
       </c>
       <c r="E8" t="n">
-        <v>9.823941952058664</v>
+        <v>9.708954067013279</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495245468408186</v>
+        <v>0.7495478661727782</v>
       </c>
       <c r="G8" t="n">
-        <v>31.38625336407353</v>
+        <v>31.1065614843517</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47812915467766</v>
+        <v>34.47920184394778</v>
       </c>
       <c r="I8" t="n">
-        <v>5.70338922775091</v>
+        <v>5.632274502563519</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684528417755116</v>
+        <v>4.684674163579864</v>
       </c>
       <c r="K8" t="n">
-        <v>11.14619942340187</v>
+        <v>11.62710418541893</v>
       </c>
       <c r="L8" t="n">
-        <v>44.77025566454895</v>
+        <v>44.70118574125034</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81029292594907</v>
+        <v>99.81265551777857</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87.11680942290202</v>
+        <v>86.46325931329331</v>
       </c>
       <c r="C9" t="n">
-        <v>43.04290001546154</v>
+        <v>42.4493691507804</v>
       </c>
       <c r="D9" t="n">
-        <v>1.950108959668872</v>
+        <v>1.925466377940446</v>
       </c>
       <c r="E9" t="n">
-        <v>10.24004844823358</v>
+        <v>10.0765316643902</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508900883954243</v>
+        <v>0.7509066038970524</v>
       </c>
       <c r="G9" t="n">
-        <v>30.18027138996594</v>
+        <v>29.77341430567922</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54094406618952</v>
+        <v>34.5417037792644</v>
       </c>
       <c r="I9" t="n">
-        <v>4.76148341797728</v>
+        <v>4.702070307765413</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693063052471401</v>
+        <v>4.693166274356577</v>
       </c>
       <c r="K9" t="n">
-        <v>12.88319057709796</v>
+        <v>13.53674068670669</v>
       </c>
       <c r="L9" t="n">
-        <v>43.91548192889187</v>
+        <v>43.85743809299725</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84157252145138</v>
+        <v>99.84354793048433</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>85.13691533635755</v>
+        <v>84.33165937369755</v>
       </c>
       <c r="C10" t="n">
-        <v>41.80274194110505</v>
+        <v>41.04778433283415</v>
       </c>
       <c r="D10" t="n">
-        <v>1.861876363832346</v>
+        <v>1.830053407854132</v>
       </c>
       <c r="E10" t="n">
-        <v>10.43908401872388</v>
+        <v>10.23128589800816</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520584397164546</v>
+        <v>0.7520714137977601</v>
       </c>
       <c r="G10" t="n">
-        <v>28.8147663116037</v>
+        <v>28.29804713175131</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59468822695691</v>
+        <v>34.59528503469696</v>
       </c>
       <c r="I10" t="n">
-        <v>3.974076727296416</v>
+        <v>3.924470151353226</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700365248227841</v>
+        <v>4.700446336236</v>
       </c>
       <c r="K10" t="n">
-        <v>14.86308466364246</v>
+        <v>15.66834062630243</v>
       </c>
       <c r="L10" t="n">
-        <v>43.20190996697532</v>
+        <v>43.15326197675883</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86773657172283</v>
+        <v>99.86938693589542</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.87063100238825</v>
+        <v>82.02071314456391</v>
       </c>
       <c r="C11" t="n">
-        <v>40.15345590092048</v>
+        <v>39.34557692107676</v>
       </c>
       <c r="D11" t="n">
-        <v>1.761596999467537</v>
+        <v>1.727562100204876</v>
       </c>
       <c r="E11" t="n">
-        <v>10.42953355796648</v>
+        <v>10.20407809567042</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530615844442876</v>
+        <v>0.7530723160606984</v>
       </c>
       <c r="G11" t="n">
-        <v>27.26282306436222</v>
+        <v>26.71322788986138</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64083288443723</v>
+        <v>34.64132653879211</v>
       </c>
       <c r="I11" t="n">
-        <v>3.316148008933701</v>
+        <v>3.274744228595063</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706634902776798</v>
+        <v>4.706701975379365</v>
       </c>
       <c r="K11" t="n">
-        <v>17.12936899761175</v>
+        <v>17.9792868554361</v>
       </c>
       <c r="L11" t="n">
-        <v>42.6067840812651</v>
+        <v>42.56612316372731</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88960897979733</v>
+        <v>99.89098694024017</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.50661361432955</v>
+        <v>79.73970206754427</v>
       </c>
       <c r="C12" t="n">
-        <v>38.30357393053372</v>
+        <v>37.57175491208259</v>
       </c>
       <c r="D12" t="n">
-        <v>1.65794195109735</v>
+        <v>1.627449403141753</v>
       </c>
       <c r="E12" t="n">
-        <v>10.27694763568516</v>
+        <v>10.06809400795576</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539242203715423</v>
+        <v>0.7539323838321434</v>
       </c>
       <c r="G12" t="n">
-        <v>25.65863706478428</v>
+        <v>25.16518901415399</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68051413709095</v>
+        <v>34.68088965627859</v>
       </c>
       <c r="I12" t="n">
-        <v>2.766622227978117</v>
+        <v>2.732070203231132</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71202637732214</v>
+        <v>4.712077398950896</v>
       </c>
       <c r="K12" t="n">
-        <v>19.49338638567046</v>
+        <v>20.26029793245575</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11092446132545</v>
+        <v>42.0769820380007</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90788477752962</v>
+        <v>99.90903488253903</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78.07765926978904</v>
+        <v>77.30675152281387</v>
       </c>
       <c r="C13" t="n">
-        <v>36.30274961461703</v>
+        <v>35.56116845924646</v>
       </c>
       <c r="D13" t="n">
-        <v>1.552348660538117</v>
+        <v>1.521525121626818</v>
       </c>
       <c r="E13" t="n">
-        <v>10.00704691379248</v>
+        <v>9.792628428170092</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546670273096043</v>
+        <v>0.7546732348421615</v>
       </c>
       <c r="G13" t="n">
-        <v>24.02445444630213</v>
+        <v>23.52728582627859</v>
       </c>
       <c r="H13" t="n">
-        <v>34.7146832562418</v>
+        <v>34.71496880273942</v>
       </c>
       <c r="I13" t="n">
-        <v>2.307790044919888</v>
+        <v>2.278962391393274</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716668920685027</v>
+        <v>4.716707717763509</v>
       </c>
       <c r="K13" t="n">
-        <v>21.92234073021094</v>
+        <v>22.69324847718615</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69805903772819</v>
+        <v>41.66969222458876</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92314938255618</v>
+        <v>99.92410916102136</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.50133552511943</v>
+        <v>83.83339365705805</v>
       </c>
       <c r="C14" t="n">
-        <v>40.12193479175602</v>
+        <v>39.61121499462814</v>
       </c>
       <c r="D14" t="n">
-        <v>1.554321237554499</v>
+        <v>1.523299429272942</v>
       </c>
       <c r="E14" t="n">
-        <v>12.18231624099659</v>
+        <v>12.05834343326632</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556259863829969</v>
+        <v>0.7555532876732801</v>
       </c>
       <c r="G14" t="n">
-        <v>25.6806544651045</v>
+        <v>25.32021097140597</v>
       </c>
       <c r="H14" t="n">
-        <v>36.38446740094732</v>
+        <v>36.52094032558703</v>
       </c>
       <c r="I14" t="n">
-        <v>3.221287779239781</v>
+        <v>2.932838161894504</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722662414893732</v>
+        <v>4.722208047958</v>
       </c>
       <c r="K14" t="n">
-        <v>15.49866447488059</v>
+        <v>16.16660634294195</v>
       </c>
       <c r="L14" t="n">
-        <v>44.27216074443251</v>
+        <v>44.12453126067302</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89276001106911</v>
+        <v>99.90235259824311</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.67839532951157</v>
+        <v>83.06642289806933</v>
       </c>
       <c r="C15" t="n">
-        <v>39.79737881488072</v>
+        <v>39.29777499622624</v>
       </c>
       <c r="D15" t="n">
-        <v>1.523499803104208</v>
+        <v>1.494732735159876</v>
       </c>
       <c r="E15" t="n">
-        <v>12.3886268469322</v>
+        <v>12.23994978617067</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564348684752338</v>
+        <v>0.7562950270480252</v>
       </c>
       <c r="G15" t="n">
-        <v>25.17141957265581</v>
+        <v>24.84537673474923</v>
       </c>
       <c r="H15" t="n">
-        <v>36.42341622569206</v>
+        <v>36.556793547172</v>
       </c>
       <c r="I15" t="n">
-        <v>2.687280084681844</v>
+        <v>2.446431148719367</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727717927970212</v>
+        <v>4.726843919050157</v>
       </c>
       <c r="K15" t="n">
-        <v>16.32160467048843</v>
+        <v>16.93357710193068</v>
       </c>
       <c r="L15" t="n">
-        <v>43.79153629854088</v>
+        <v>43.68718017512378</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91051978391002</v>
+        <v>99.91853227328069</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.12739264236554</v>
+        <v>80.60601588907117</v>
       </c>
       <c r="C16" t="n">
-        <v>37.6622117491161</v>
+        <v>37.21572937811847</v>
       </c>
       <c r="D16" t="n">
-        <v>1.425371714275919</v>
+        <v>1.400588352616085</v>
       </c>
       <c r="E16" t="n">
-        <v>11.96425680949873</v>
+        <v>11.80909648096566</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571315178309512</v>
+        <v>0.7569331738253954</v>
       </c>
       <c r="G16" t="n">
-        <v>23.55013725235167</v>
+        <v>23.28051326669208</v>
       </c>
       <c r="H16" t="n">
-        <v>36.45696088433241</v>
+        <v>36.5876394461384</v>
       </c>
       <c r="I16" t="n">
-        <v>2.241462477632409</v>
+        <v>2.04041283242484</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732071986443446</v>
+        <v>4.73083233640872</v>
       </c>
       <c r="K16" t="n">
-        <v>18.87260735763448</v>
+        <v>19.39398411092883</v>
       </c>
       <c r="L16" t="n">
-        <v>43.39053422423047</v>
+        <v>43.32233009015496</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92535333098105</v>
+        <v>99.93204357920224</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.66745044854045</v>
+        <v>82.13947635067356</v>
       </c>
       <c r="C17" t="n">
-        <v>38.77252311321048</v>
+        <v>38.34192851430615</v>
       </c>
       <c r="D17" t="n">
-        <v>1.426684591704273</v>
+        <v>1.401745015599055</v>
       </c>
       <c r="E17" t="n">
-        <v>12.70394285624714</v>
+        <v>12.53628492250432</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7578288944311038</v>
+        <v>0.7575582801109861</v>
       </c>
       <c r="G17" t="n">
-        <v>23.91977925896409</v>
+        <v>23.6780046243902</v>
       </c>
       <c r="H17" t="n">
-        <v>36.8384910722862</v>
+        <v>36.9961203713513</v>
       </c>
       <c r="I17" t="n">
-        <v>2.284293184713249</v>
+        <v>2.035023886024032</v>
       </c>
       <c r="J17" t="n">
-        <v>4.7364305901944</v>
+        <v>4.734739250693663</v>
       </c>
       <c r="K17" t="n">
-        <v>17.33254955145955</v>
+        <v>17.86052364932644</v>
       </c>
       <c r="L17" t="n">
-        <v>43.81885429831498</v>
+        <v>43.72976968079841</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92392696298501</v>
+        <v>99.932221844431</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.18505229096719</v>
+        <v>79.78406725864461</v>
       </c>
       <c r="C18" t="n">
-        <v>36.64310038609462</v>
+        <v>36.30082595696784</v>
       </c>
       <c r="D18" t="n">
-        <v>1.334664233688946</v>
+        <v>1.314903362335937</v>
       </c>
       <c r="E18" t="n">
-        <v>12.20205984900624</v>
+        <v>12.04247293219132</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7584290597441181</v>
+        <v>0.7580954042889988</v>
       </c>
       <c r="G18" t="n">
-        <v>22.3769668785289</v>
+        <v>22.21109227965464</v>
       </c>
       <c r="H18" t="n">
-        <v>36.86766544751502</v>
+        <v>37.02235137068934</v>
       </c>
       <c r="I18" t="n">
-        <v>1.905085199083233</v>
+        <v>1.69705563267812</v>
       </c>
       <c r="J18" t="n">
-        <v>4.740181623400741</v>
+        <v>4.738096276806242</v>
       </c>
       <c r="K18" t="n">
-        <v>19.81494770903282</v>
+        <v>20.21593274135538</v>
       </c>
       <c r="L18" t="n">
-        <v>43.4784993164083</v>
+        <v>43.42671286039832</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93654741153574</v>
+        <v>99.94347155872155</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.12593305014867</v>
+        <v>78.81061532249868</v>
       </c>
       <c r="C19" t="n">
-        <v>35.87759594668904</v>
+        <v>35.58881421353027</v>
       </c>
       <c r="D19" t="n">
-        <v>1.296170947880141</v>
+        <v>1.279682005894082</v>
       </c>
       <c r="E19" t="n">
-        <v>12.11491034058759</v>
+        <v>11.95574324161406</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7589366328165914</v>
+        <v>0.758549129148206</v>
       </c>
       <c r="G19" t="n">
-        <v>21.73158884272989</v>
+        <v>21.61613996562689</v>
       </c>
       <c r="H19" t="n">
-        <v>36.89233886157489</v>
+        <v>37.0445094804314</v>
       </c>
       <c r="I19" t="n">
-        <v>1.588633469455884</v>
+        <v>1.415059442607773</v>
       </c>
       <c r="J19" t="n">
-        <v>4.743353955103698</v>
+        <v>4.740932057176287</v>
       </c>
       <c r="K19" t="n">
-        <v>20.87406694985132</v>
+        <v>21.18938467750131</v>
       </c>
       <c r="L19" t="n">
-        <v>43.19541807015179</v>
+        <v>43.17466067472735</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94708096669214</v>
+        <v>99.95285956575893</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.48066294844087</v>
+        <v>76.23171136559796</v>
       </c>
       <c r="C20" t="n">
-        <v>33.47698019973082</v>
+        <v>33.22774641907802</v>
       </c>
       <c r="D20" t="n">
-        <v>1.199297145759414</v>
+        <v>1.185600974154509</v>
       </c>
       <c r="E20" t="n">
-        <v>11.43023169127783</v>
+        <v>11.27340553559593</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7593747857627148</v>
+        <v>0.7589404601184039</v>
       </c>
       <c r="G20" t="n">
-        <v>20.10740366811025</v>
+        <v>20.02694144534892</v>
       </c>
       <c r="H20" t="n">
-        <v>36.91363772403933</v>
+        <v>37.06362052186356</v>
       </c>
       <c r="I20" t="n">
-        <v>1.32462552247437</v>
+        <v>1.179824552776602</v>
       </c>
       <c r="J20" t="n">
-        <v>4.746092411016969</v>
+        <v>4.743377875740023</v>
       </c>
       <c r="K20" t="n">
-        <v>23.51933705155914</v>
+        <v>23.76828863440204</v>
       </c>
       <c r="L20" t="n">
-        <v>42.95955404122516</v>
+        <v>42.96465773978083</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95587129251511</v>
+        <v>99.9606927932609</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.3880155994807</v>
+        <v>81.82866484498609</v>
       </c>
       <c r="C21" t="n">
-        <v>37.02877631310339</v>
+        <v>36.68602066838418</v>
       </c>
       <c r="D21" t="n">
-        <v>1.200285401112407</v>
+        <v>1.186422616923897</v>
       </c>
       <c r="E21" t="n">
-        <v>13.37706570828304</v>
+        <v>13.1447485540299</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7600005324340977</v>
+        <v>0.7594664194884163</v>
       </c>
       <c r="G21" t="n">
-        <v>21.72193744830796</v>
+        <v>21.62080714917411</v>
       </c>
       <c r="H21" t="n">
-        <v>38.54202032463</v>
+        <v>38.66929295028054</v>
       </c>
       <c r="I21" t="n">
-        <v>2.036702857000067</v>
+        <v>1.701262033286607</v>
       </c>
       <c r="J21" t="n">
-        <v>4.750003327713112</v>
+        <v>4.746665121802601</v>
       </c>
       <c r="K21" t="n">
-        <v>17.61198440051932</v>
+        <v>18.17133515501394</v>
       </c>
       <c r="L21" t="n">
-        <v>45.29140508847469</v>
+        <v>45.08597471511363</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9321658020974</v>
+        <v>99.94333053851174</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_75_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_75_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.22471302949244</v>
+        <v>45.35928231878275</v>
       </c>
       <c r="M2" t="n">
-        <v>99.66822322223607</v>
+        <v>100.5633776494525</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.1176636498035</v>
+        <v>87.99307004865751</v>
       </c>
       <c r="C3" t="n">
-        <v>45.95744078166845</v>
+        <v>45.86968099084735</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22894039065265</v>
+        <v>2.228687518841031</v>
       </c>
       <c r="E3" t="n">
-        <v>5.727762075840063</v>
+        <v>5.670942988164597</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429801302175502</v>
+        <v>0.742895839613677</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98214907382646</v>
+        <v>33.95296761901452</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1770859900073</v>
+        <v>34.17320862222913</v>
       </c>
       <c r="I3" t="n">
-        <v>6.615120175399799</v>
+        <v>6.581268463209087</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643625813859688</v>
+        <v>4.643098997585481</v>
       </c>
       <c r="K3" t="n">
-        <v>11.8823363501965</v>
+        <v>12.00692995134246</v>
       </c>
       <c r="L3" t="n">
-        <v>48.92279632400165</v>
+        <v>48.88715070110663</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7625734558666</v>
+        <v>106.7637616432964</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.2728860755107</v>
+        <v>87.05030287898325</v>
       </c>
       <c r="C4" t="n">
-        <v>42.75582078727166</v>
+        <v>42.56679186029413</v>
       </c>
       <c r="D4" t="n">
-        <v>2.188650880996126</v>
+        <v>2.183068970898835</v>
       </c>
       <c r="E4" t="n">
-        <v>6.544934386449198</v>
+        <v>6.470854336948935</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445477779234894</v>
+        <v>0.7444592671617205</v>
       </c>
       <c r="G4" t="n">
-        <v>33.36790020068432</v>
+        <v>33.25799128517958</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2491977844805</v>
+        <v>34.24512628943913</v>
       </c>
       <c r="I4" t="n">
-        <v>5.524231432955242</v>
+        <v>5.495932309594287</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653423612021808</v>
+        <v>4.652870419760753</v>
       </c>
       <c r="K4" t="n">
-        <v>12.72711392448931</v>
+        <v>12.94969712101675</v>
       </c>
       <c r="L4" t="n">
-        <v>44.33331195003348</v>
+        <v>44.30069800582218</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81624666179445</v>
+        <v>99.81718698713307</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.24831019926383</v>
+        <v>85.863762627843</v>
       </c>
       <c r="C5" t="n">
-        <v>42.5887117354945</v>
+        <v>42.23315754093692</v>
       </c>
       <c r="D5" t="n">
-        <v>2.139194180216791</v>
+        <v>2.125043865419704</v>
       </c>
       <c r="E5" t="n">
-        <v>7.165661110157789</v>
+        <v>7.063545131275586</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458748200664155</v>
+        <v>0.7457852648195537</v>
       </c>
       <c r="G5" t="n">
-        <v>32.61388946731926</v>
+        <v>32.3740070968321</v>
       </c>
       <c r="H5" t="n">
-        <v>34.3102417230551</v>
+        <v>34.30612218169946</v>
       </c>
       <c r="I5" t="n">
-        <v>4.611731273033387</v>
+        <v>4.588101182674386</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661717625415097</v>
+        <v>4.66115790512221</v>
       </c>
       <c r="K5" t="n">
-        <v>13.75168980073618</v>
+        <v>14.136237372157</v>
       </c>
       <c r="L5" t="n">
-        <v>43.50614759063168</v>
+        <v>43.47794030052846</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84654912686234</v>
+        <v>99.84733521362237</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.92993381455989</v>
+        <v>84.50962421317359</v>
       </c>
       <c r="C6" t="n">
-        <v>41.98676142542207</v>
+        <v>41.59147921904901</v>
       </c>
       <c r="D6" t="n">
-        <v>2.075044780819192</v>
+        <v>2.058913457558913</v>
       </c>
       <c r="E6" t="n">
-        <v>7.592265610411848</v>
+        <v>7.481929518549599</v>
       </c>
       <c r="F6" t="n">
-        <v>0.747001556176634</v>
+        <v>0.7469116671986162</v>
       </c>
       <c r="G6" t="n">
-        <v>31.63587567095779</v>
+        <v>31.36654257892729</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36207158412515</v>
+        <v>34.35793669113634</v>
       </c>
       <c r="I6" t="n">
-        <v>3.848914885965311</v>
+        <v>3.829192379811483</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668759726103962</v>
+        <v>4.668197919991352</v>
       </c>
       <c r="K6" t="n">
-        <v>15.07006618544012</v>
+        <v>15.49037578682639</v>
       </c>
       <c r="L6" t="n">
-        <v>42.81506874266469</v>
+        <v>42.79069773905032</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87189635352686</v>
+        <v>99.87255274492573</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.53268545275357</v>
+        <v>83.01878985392328</v>
       </c>
       <c r="C7" t="n">
-        <v>41.18751076849878</v>
+        <v>40.6952951379579</v>
       </c>
       <c r="D7" t="n">
-        <v>2.007417259228538</v>
+        <v>1.986423205616853</v>
       </c>
       <c r="E7" t="n">
-        <v>7.88008363576562</v>
+        <v>7.751020196662139</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479588760690371</v>
+        <v>0.7478698631236336</v>
       </c>
       <c r="G7" t="n">
-        <v>30.60483485451221</v>
+        <v>30.2621889375685</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40610829917569</v>
+        <v>34.40201370368714</v>
       </c>
       <c r="I7" t="n">
-        <v>3.211539552570981</v>
+        <v>3.19508730274232</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674742975431482</v>
+        <v>4.67418664452271</v>
       </c>
       <c r="K7" t="n">
-        <v>16.46731454724643</v>
+        <v>16.98121014607672</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23826038186687</v>
+        <v>42.21712826097059</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89308569761208</v>
+        <v>99.89363354500522</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.37289581458106</v>
+        <v>87.82728419087306</v>
       </c>
       <c r="C8" t="n">
-        <v>43.48436559110929</v>
+        <v>42.94549822016928</v>
       </c>
       <c r="D8" t="n">
-        <v>2.011681886952134</v>
+        <v>1.990667971245539</v>
       </c>
       <c r="E8" t="n">
-        <v>9.708954067013279</v>
+        <v>9.548840435027332</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495478661727782</v>
+        <v>0.7494679779063953</v>
       </c>
       <c r="G8" t="n">
-        <v>31.1065614843517</v>
+        <v>30.74829159292615</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47920184394778</v>
+        <v>34.47552698369418</v>
       </c>
       <c r="I8" t="n">
-        <v>5.632274502563519</v>
+        <v>5.6303143681585</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684674163579864</v>
+        <v>4.684174861914971</v>
       </c>
       <c r="K8" t="n">
-        <v>11.62710418541893</v>
+        <v>12.17271580912693</v>
       </c>
       <c r="L8" t="n">
-        <v>44.70118574125034</v>
+        <v>44.69450901513948</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81265551777857</v>
+        <v>99.81272304443569</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.46325931329331</v>
+        <v>85.85468232241924</v>
       </c>
       <c r="C9" t="n">
-        <v>42.4493691507804</v>
+        <v>41.84665421534029</v>
       </c>
       <c r="D9" t="n">
-        <v>1.925466377940446</v>
+        <v>1.901272610648628</v>
       </c>
       <c r="E9" t="n">
-        <v>10.0765316643902</v>
+        <v>9.903443794771819</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7509066038970524</v>
+        <v>0.7508357416769562</v>
       </c>
       <c r="G9" t="n">
-        <v>29.77341430567922</v>
+        <v>29.36747135851573</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5417037792644</v>
+        <v>34.53844411713998</v>
       </c>
       <c r="I9" t="n">
-        <v>4.702070307765413</v>
+        <v>4.700491314185158</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693166274356577</v>
+        <v>4.692723385480977</v>
       </c>
       <c r="K9" t="n">
-        <v>13.53674068670669</v>
+        <v>14.14531767758074</v>
       </c>
       <c r="L9" t="n">
-        <v>43.85743809299725</v>
+        <v>43.85163048574123</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84354793048433</v>
+        <v>99.84360237866227</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.33165937369755</v>
+        <v>83.74367288182087</v>
       </c>
       <c r="C10" t="n">
-        <v>41.04778433283415</v>
+        <v>40.46486008087379</v>
       </c>
       <c r="D10" t="n">
-        <v>1.830053407854132</v>
+        <v>1.806605996064508</v>
       </c>
       <c r="E10" t="n">
-        <v>10.23128589800816</v>
+        <v>10.06420509378354</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520714137977601</v>
+        <v>0.7520082376158759</v>
       </c>
       <c r="G10" t="n">
-        <v>28.29804713175131</v>
+        <v>27.90523018550565</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59528503469696</v>
+        <v>34.59237893033028</v>
       </c>
       <c r="I10" t="n">
-        <v>3.924470151353226</v>
+        <v>3.923192953421794</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700446336236</v>
+        <v>4.700051485099225</v>
       </c>
       <c r="K10" t="n">
-        <v>15.66834062630243</v>
+        <v>16.25632711817913</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15326197675883</v>
+        <v>43.14824359777526</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86938693589542</v>
+        <v>99.86943079682818</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.02071314456391</v>
+        <v>81.48967353166782</v>
       </c>
       <c r="C11" t="n">
-        <v>39.34557692107676</v>
+        <v>38.81893807301401</v>
       </c>
       <c r="D11" t="n">
-        <v>1.727562100204876</v>
+        <v>1.706512730515312</v>
       </c>
       <c r="E11" t="n">
-        <v>10.20407809567042</v>
+        <v>10.05222507607344</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530723160606984</v>
+        <v>0.75301525824224</v>
       </c>
       <c r="G11" t="n">
-        <v>26.71322788986138</v>
+        <v>26.35916777828805</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64132653879211</v>
+        <v>34.63870187914304</v>
       </c>
       <c r="I11" t="n">
-        <v>3.274744228595063</v>
+        <v>3.273705445391743</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706701975379365</v>
+        <v>4.706345364014001</v>
       </c>
       <c r="K11" t="n">
-        <v>17.9792868554361</v>
+        <v>18.51032646833216</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56612316372731</v>
+        <v>42.56175787661434</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89098694024017</v>
+        <v>99.89102241796051</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.73970206754427</v>
+        <v>79.12014607300165</v>
       </c>
       <c r="C12" t="n">
-        <v>37.57175491208259</v>
+        <v>36.9560746963128</v>
       </c>
       <c r="D12" t="n">
-        <v>1.627449403141753</v>
+        <v>1.602272158206713</v>
       </c>
       <c r="E12" t="n">
-        <v>10.06809400795576</v>
+        <v>9.893399760243225</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539323838321434</v>
+        <v>0.7538817276559888</v>
       </c>
       <c r="G12" t="n">
-        <v>25.16518901415399</v>
+        <v>24.74904516645297</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68088965627859</v>
+        <v>34.67855947217548</v>
       </c>
       <c r="I12" t="n">
-        <v>2.732070203231132</v>
+        <v>2.731226990417338</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712077398950896</v>
+        <v>4.711760797849931</v>
       </c>
       <c r="K12" t="n">
-        <v>20.26029793245575</v>
+        <v>20.87985392699836</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0769820380007</v>
+        <v>42.07313511431682</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90903488253903</v>
+        <v>99.90906373762799</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.30675152281387</v>
+        <v>76.66599153039654</v>
       </c>
       <c r="C13" t="n">
-        <v>35.56116845924646</v>
+        <v>34.92378135195621</v>
       </c>
       <c r="D13" t="n">
-        <v>1.521525121626818</v>
+        <v>1.495260902135947</v>
       </c>
       <c r="E13" t="n">
-        <v>9.792628428170092</v>
+        <v>9.612360224123664</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546732348421615</v>
+        <v>0.754628495723157</v>
       </c>
       <c r="G13" t="n">
-        <v>23.52728582627859</v>
+        <v>23.09612596901873</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71496880273942</v>
+        <v>34.71291080326522</v>
       </c>
       <c r="I13" t="n">
-        <v>2.278962391393274</v>
+        <v>2.278277037860092</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716707717763509</v>
+        <v>4.716428098269732</v>
       </c>
       <c r="K13" t="n">
-        <v>22.69324847718615</v>
+        <v>23.33400846960346</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66969222458876</v>
+        <v>41.66634276203986</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92410916102136</v>
+        <v>99.92413258359953</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.83339365705805</v>
+        <v>83.50593171030651</v>
       </c>
       <c r="C14" t="n">
-        <v>39.61121499462814</v>
+        <v>39.04426745733036</v>
       </c>
       <c r="D14" t="n">
-        <v>1.523299429272942</v>
+        <v>1.497141438280571</v>
       </c>
       <c r="E14" t="n">
-        <v>12.05834343326632</v>
+        <v>11.93252067623441</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555532876732801</v>
+        <v>0.7555775649858816</v>
       </c>
       <c r="G14" t="n">
-        <v>25.32021097140597</v>
+        <v>24.90813235622716</v>
       </c>
       <c r="H14" t="n">
-        <v>36.52094032558703</v>
+        <v>36.5395272051767</v>
       </c>
       <c r="I14" t="n">
-        <v>2.932838161894504</v>
+        <v>3.150672688240032</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722208047958</v>
+        <v>4.72235978116176</v>
       </c>
       <c r="K14" t="n">
-        <v>16.16660634294195</v>
+        <v>16.49406828969347</v>
       </c>
       <c r="L14" t="n">
-        <v>44.12453126067302</v>
+        <v>44.35677374707171</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90235259824311</v>
+        <v>99.89510949409555</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.06642289806933</v>
+        <v>82.70915509101687</v>
       </c>
       <c r="C15" t="n">
-        <v>39.29777499622624</v>
+        <v>38.73418884536058</v>
       </c>
       <c r="D15" t="n">
-        <v>1.494732735159876</v>
+        <v>1.467579179208668</v>
       </c>
       <c r="E15" t="n">
-        <v>12.23994978617067</v>
+        <v>12.13496043915335</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562950270480252</v>
+        <v>0.7563779262274752</v>
       </c>
       <c r="G15" t="n">
-        <v>24.84537673474923</v>
+        <v>24.41630129545731</v>
       </c>
       <c r="H15" t="n">
-        <v>36.556793547172</v>
+        <v>36.57823245890102</v>
       </c>
       <c r="I15" t="n">
-        <v>2.446431148719367</v>
+        <v>2.628341753147331</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726843919050157</v>
+        <v>4.72736203892172</v>
       </c>
       <c r="K15" t="n">
-        <v>16.93357710193068</v>
+        <v>17.29084490898314</v>
       </c>
       <c r="L15" t="n">
-        <v>43.68718017512378</v>
+        <v>43.88744755987182</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91853227328069</v>
+        <v>99.91248131421554</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.60601588907117</v>
+        <v>80.18861603513361</v>
       </c>
       <c r="C16" t="n">
-        <v>37.21572937811847</v>
+        <v>36.61972724987844</v>
       </c>
       <c r="D16" t="n">
-        <v>1.400588352616085</v>
+        <v>1.371531670753833</v>
       </c>
       <c r="E16" t="n">
-        <v>11.80909648096566</v>
+        <v>11.70615329404371</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569331738253954</v>
+        <v>0.7570672147619066</v>
       </c>
       <c r="G16" t="n">
-        <v>23.28051326669208</v>
+        <v>22.81834669216581</v>
       </c>
       <c r="H16" t="n">
-        <v>36.5876394461384</v>
+        <v>36.61156626647185</v>
       </c>
       <c r="I16" t="n">
-        <v>2.04041283242484</v>
+        <v>2.192280804674585</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73083233640872</v>
+        <v>4.731670092261917</v>
       </c>
       <c r="K16" t="n">
-        <v>19.39398411092883</v>
+        <v>19.8113839648664</v>
       </c>
       <c r="L16" t="n">
-        <v>43.32233009015496</v>
+        <v>43.49587929211218</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93204357920224</v>
+        <v>99.92699050685702</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.13947635067356</v>
+        <v>81.81302560405742</v>
       </c>
       <c r="C17" t="n">
-        <v>38.34192851430615</v>
+        <v>37.78754309934295</v>
       </c>
       <c r="D17" t="n">
-        <v>1.401745015599055</v>
+        <v>1.372776896105104</v>
       </c>
       <c r="E17" t="n">
-        <v>12.53628492250432</v>
+        <v>12.47021537722866</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575582801109861</v>
+        <v>0.757754562570594</v>
       </c>
       <c r="G17" t="n">
-        <v>23.6780046243902</v>
+        <v>23.22110389747499</v>
       </c>
       <c r="H17" t="n">
-        <v>36.9961203713513</v>
+        <v>37.02684645397373</v>
       </c>
       <c r="I17" t="n">
-        <v>2.035023886024032</v>
+        <v>2.228362400638114</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734739250693663</v>
+        <v>4.735966016066213</v>
       </c>
       <c r="K17" t="n">
-        <v>17.86052364932644</v>
+        <v>18.18697439594259</v>
       </c>
       <c r="L17" t="n">
-        <v>43.72976968079841</v>
+        <v>43.95127113516459</v>
       </c>
       <c r="M17" t="n">
-        <v>99.932221844431</v>
+        <v>99.92578863045013</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.78406725864461</v>
+        <v>79.41717832409051</v>
       </c>
       <c r="C18" t="n">
-        <v>36.30082595696784</v>
+        <v>35.73549823127889</v>
       </c>
       <c r="D18" t="n">
-        <v>1.314903362335937</v>
+        <v>1.285041285502804</v>
       </c>
       <c r="E18" t="n">
-        <v>12.04247293219132</v>
+        <v>11.98296703008406</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580954042889988</v>
+        <v>0.7583456286770617</v>
       </c>
       <c r="G18" t="n">
-        <v>22.21109227965464</v>
+        <v>21.73701880317833</v>
       </c>
       <c r="H18" t="n">
-        <v>37.02235137068934</v>
+        <v>37.05572825165513</v>
       </c>
       <c r="I18" t="n">
-        <v>1.69705563267812</v>
+        <v>1.8584171457615</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738096276806242</v>
+        <v>4.739660179231636</v>
       </c>
       <c r="K18" t="n">
-        <v>20.21593274135538</v>
+        <v>20.58282167590946</v>
       </c>
       <c r="L18" t="n">
-        <v>43.42671286039832</v>
+        <v>43.61978113723838</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94347155872155</v>
+        <v>99.93810104442673</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.81061532249868</v>
+        <v>78.4225010025788</v>
       </c>
       <c r="C19" t="n">
-        <v>35.58881421353027</v>
+        <v>35.02680891839739</v>
       </c>
       <c r="D19" t="n">
-        <v>1.279682005894082</v>
+        <v>1.2493488907396</v>
       </c>
       <c r="E19" t="n">
-        <v>11.95574324161406</v>
+        <v>11.90842015323551</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758549129148206</v>
+        <v>0.7588451490166331</v>
       </c>
       <c r="G19" t="n">
-        <v>21.61613996562689</v>
+        <v>21.13326679547948</v>
       </c>
       <c r="H19" t="n">
-        <v>37.0445094804314</v>
+        <v>37.08013676574075</v>
       </c>
       <c r="I19" t="n">
-        <v>1.415059442607773</v>
+        <v>1.549701067012854</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740932057176287</v>
+        <v>4.742782181353958</v>
       </c>
       <c r="K19" t="n">
-        <v>21.18938467750131</v>
+        <v>21.5774989974212</v>
       </c>
       <c r="L19" t="n">
-        <v>43.17466067472735</v>
+        <v>43.34406938568802</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95285956575893</v>
+        <v>99.94837730150661</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.23171136559796</v>
+        <v>75.83536018243942</v>
       </c>
       <c r="C20" t="n">
-        <v>33.22774641907802</v>
+        <v>32.6779764276392</v>
       </c>
       <c r="D20" t="n">
-        <v>1.185600974154509</v>
+        <v>1.155745858674206</v>
       </c>
       <c r="E20" t="n">
-        <v>11.27340553559593</v>
+        <v>11.231582538352</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589404601184039</v>
+        <v>0.7592761452086018</v>
       </c>
       <c r="G20" t="n">
-        <v>20.02694144534892</v>
+        <v>19.54993177660197</v>
       </c>
       <c r="H20" t="n">
-        <v>37.06362052186356</v>
+        <v>37.10119692243335</v>
       </c>
       <c r="I20" t="n">
-        <v>1.179824552776602</v>
+        <v>1.29215103361554</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743377875740023</v>
+        <v>4.745475907553761</v>
       </c>
       <c r="K20" t="n">
-        <v>23.76828863440204</v>
+        <v>24.16463981756057</v>
       </c>
       <c r="L20" t="n">
-        <v>42.96465773978083</v>
+        <v>43.11433650293876</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9606927932609</v>
+        <v>99.95695274813853</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.82866484498609</v>
+        <v>81.64417481640399</v>
       </c>
       <c r="C21" t="n">
-        <v>36.68602066838418</v>
+        <v>36.21139984451894</v>
       </c>
       <c r="D21" t="n">
-        <v>1.186422616923897</v>
+        <v>1.156654869712328</v>
       </c>
       <c r="E21" t="n">
-        <v>13.1447485540299</v>
+        <v>13.15976619803891</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594664194884163</v>
+        <v>0.7598733270127134</v>
       </c>
       <c r="G21" t="n">
-        <v>21.62080714917411</v>
+        <v>21.16358624587248</v>
       </c>
       <c r="H21" t="n">
-        <v>38.66929295028054</v>
+        <v>38.72865571869394</v>
       </c>
       <c r="I21" t="n">
-        <v>1.701262033286607</v>
+        <v>1.926430163244173</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746665121802601</v>
+        <v>4.749208293829458</v>
       </c>
       <c r="K21" t="n">
-        <v>18.17133515501394</v>
+        <v>18.355825183596</v>
       </c>
       <c r="L21" t="n">
-        <v>45.08597471511363</v>
+        <v>45.36861109893569</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94333053851174</v>
+        <v>99.93583612705062</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_75_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_75_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.35928231878275</v>
+        <v>43.77126897141857</v>
       </c>
       <c r="M2" t="n">
-        <v>100.5633776494525</v>
+        <v>96.09021358528759</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.99307004865751</v>
+        <v>81.43540185332141</v>
       </c>
       <c r="C3" t="n">
-        <v>45.86968099084735</v>
+        <v>43.19095740887698</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228687518841031</v>
+        <v>2.17765720216401</v>
       </c>
       <c r="E3" t="n">
-        <v>5.670942988164597</v>
+        <v>4.151406536722148</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742895839613677</v>
+        <v>0.7376036754464722</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95296761901452</v>
+        <v>32.75559374921699</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17320862222913</v>
+        <v>33.92976907053772</v>
       </c>
       <c r="I3" t="n">
-        <v>6.581268463209087</v>
+        <v>3.073348647693634</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643098997585481</v>
+        <v>4.610022971540451</v>
       </c>
       <c r="K3" t="n">
-        <v>12.00692995134246</v>
+        <v>18.56459814667858</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88715070110663</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7637616432964</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.05030287898325</v>
+        <v>88.44689617197592</v>
       </c>
       <c r="C4" t="n">
-        <v>42.56679186029413</v>
+        <v>42.76073370113382</v>
       </c>
       <c r="D4" t="n">
-        <v>2.183068970898835</v>
+        <v>2.183347882260713</v>
       </c>
       <c r="E4" t="n">
-        <v>6.470854336948935</v>
+        <v>6.51157346392414</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444592671617205</v>
+        <v>0.7395311902779834</v>
       </c>
       <c r="G4" t="n">
-        <v>33.25799128517958</v>
+        <v>33.4380240303303</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24512628943913</v>
+        <v>34.01843475278723</v>
       </c>
       <c r="I4" t="n">
-        <v>5.495932309594287</v>
+        <v>6.933914913158163</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652870419760753</v>
+        <v>4.622069939237396</v>
       </c>
       <c r="K4" t="n">
-        <v>12.94969712101675</v>
+        <v>11.55310382802407</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30069800582218</v>
+        <v>45.45563439249489</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81718698713307</v>
+        <v>99.76947192165279</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.863762627843</v>
+        <v>87.20246221371819</v>
       </c>
       <c r="C5" t="n">
-        <v>42.23315754093692</v>
+        <v>42.59108634647403</v>
       </c>
       <c r="D5" t="n">
-        <v>2.125043865419704</v>
+        <v>2.123551164779497</v>
       </c>
       <c r="E5" t="n">
-        <v>7.063545131275586</v>
+        <v>7.298412491407761</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457852648195537</v>
+        <v>0.7411682482741442</v>
       </c>
       <c r="G5" t="n">
-        <v>32.3740070968321</v>
+        <v>32.52223589948904</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30612218169946</v>
+        <v>34.09373942061062</v>
       </c>
       <c r="I5" t="n">
-        <v>4.588101182674386</v>
+        <v>5.791053437443727</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66115790512221</v>
+        <v>4.632301551713401</v>
       </c>
       <c r="K5" t="n">
-        <v>14.136237372157</v>
+        <v>12.79753778628181</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47794030052846</v>
+        <v>44.41876711965643</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84733521362237</v>
+        <v>99.80739125241227</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.50962421317359</v>
+        <v>85.65183034275996</v>
       </c>
       <c r="C6" t="n">
-        <v>41.59147921904901</v>
+        <v>41.93904891041495</v>
       </c>
       <c r="D6" t="n">
-        <v>2.058913457558913</v>
+        <v>2.048893790792751</v>
       </c>
       <c r="E6" t="n">
-        <v>7.481929518549599</v>
+        <v>7.847649682683261</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469116671986162</v>
+        <v>0.7425628546430949</v>
       </c>
       <c r="G6" t="n">
-        <v>31.36654257892729</v>
+        <v>31.3788564656879</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35793669113634</v>
+        <v>34.15789131358236</v>
       </c>
       <c r="I6" t="n">
-        <v>3.829192379811483</v>
+        <v>4.834958393851251</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668197919991352</v>
+        <v>4.641017841519344</v>
       </c>
       <c r="K6" t="n">
-        <v>15.49037578682639</v>
+        <v>14.34816965724004</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79069773905032</v>
+        <v>43.55191883686047</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87255274492573</v>
+        <v>99.83913740451545</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.01878985392328</v>
+        <v>83.93006789826187</v>
       </c>
       <c r="C7" t="n">
-        <v>40.6952951379579</v>
+        <v>40.96772234845493</v>
       </c>
       <c r="D7" t="n">
-        <v>1.986423205616853</v>
+        <v>1.966573113482103</v>
       </c>
       <c r="E7" t="n">
-        <v>7.751020196662139</v>
+        <v>8.204944248152431</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478698631236336</v>
+        <v>0.7437530038148983</v>
       </c>
       <c r="G7" t="n">
-        <v>30.2621889375685</v>
+        <v>30.1181133617276</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40201370368714</v>
+        <v>34.21263817548532</v>
       </c>
       <c r="I7" t="n">
-        <v>3.19508730274232</v>
+        <v>4.035589721756407</v>
       </c>
       <c r="J7" t="n">
-        <v>4.67418664452271</v>
+        <v>4.648456273843115</v>
       </c>
       <c r="K7" t="n">
-        <v>16.98121014607672</v>
+        <v>16.06993210173813</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21712826097059</v>
+        <v>42.82804114997775</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89363354500522</v>
+        <v>99.86569560017081</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.82728419087306</v>
+        <v>82.02527911180651</v>
       </c>
       <c r="C8" t="n">
-        <v>42.94549822016928</v>
+        <v>39.68909351318784</v>
       </c>
       <c r="D8" t="n">
-        <v>1.990667971245539</v>
+        <v>1.876162714309613</v>
       </c>
       <c r="E8" t="n">
-        <v>9.548840435027332</v>
+        <v>8.388999242567445</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494679779063953</v>
+        <v>0.7447708436789418</v>
       </c>
       <c r="G8" t="n">
-        <v>30.74829159292615</v>
+        <v>28.73347597769735</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47552698369418</v>
+        <v>34.25945880923132</v>
       </c>
       <c r="I8" t="n">
-        <v>5.6303143681585</v>
+        <v>3.367593751328456</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684174861914971</v>
+        <v>4.654817772993386</v>
       </c>
       <c r="K8" t="n">
-        <v>12.17271580912693</v>
+        <v>17.97472088819348</v>
       </c>
       <c r="L8" t="n">
-        <v>44.69450901513948</v>
+        <v>42.22408588412544</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81272304443569</v>
+        <v>99.88790028550677</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.85468232241924</v>
+        <v>79.91141601910546</v>
       </c>
       <c r="C9" t="n">
-        <v>41.84665421534029</v>
+        <v>38.09726703990349</v>
       </c>
       <c r="D9" t="n">
-        <v>1.901272610648628</v>
+        <v>1.776547734401394</v>
       </c>
       <c r="E9" t="n">
-        <v>9.903443794771819</v>
+        <v>8.411854299021643</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508357416769562</v>
+        <v>0.7456436938816772</v>
       </c>
       <c r="G9" t="n">
-        <v>29.36747135851573</v>
+        <v>27.20787022379296</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53844411713998</v>
+        <v>34.29960991855715</v>
       </c>
       <c r="I9" t="n">
-        <v>4.700491314185158</v>
+        <v>2.809617062690163</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692723385480977</v>
+        <v>4.660273086760482</v>
       </c>
       <c r="K9" t="n">
-        <v>14.14531767758074</v>
+        <v>20.08858398089452</v>
       </c>
       <c r="L9" t="n">
-        <v>43.85163048574123</v>
+        <v>41.72060470833175</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84360237866227</v>
+        <v>99.90645572912976</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.74367288182087</v>
+        <v>85.05315627472244</v>
       </c>
       <c r="C10" t="n">
-        <v>40.46486008087379</v>
+        <v>41.68377528791623</v>
       </c>
       <c r="D10" t="n">
-        <v>1.806605996064508</v>
+        <v>1.778483634407152</v>
       </c>
       <c r="E10" t="n">
-        <v>10.06420509378354</v>
+        <v>10.42558569884149</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520082376158759</v>
+        <v>0.7464562201106815</v>
       </c>
       <c r="G10" t="n">
-        <v>27.90523018550565</v>
+        <v>28.77867244921709</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59237893033028</v>
+        <v>35.87813999651802</v>
       </c>
       <c r="I10" t="n">
-        <v>3.923192953421794</v>
+        <v>2.780466899936257</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700051485099225</v>
+        <v>4.665351375691759</v>
       </c>
       <c r="K10" t="n">
-        <v>16.25632711817913</v>
+        <v>14.94684372527754</v>
       </c>
       <c r="L10" t="n">
-        <v>43.14824359777526</v>
+        <v>43.27679964248765</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86943079682818</v>
+        <v>99.90741865568143</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.48967353166782</v>
+        <v>84.47714526168676</v>
       </c>
       <c r="C11" t="n">
-        <v>38.81893807301401</v>
+        <v>41.41456808843988</v>
       </c>
       <c r="D11" t="n">
-        <v>1.706512730515312</v>
+        <v>1.745067754965459</v>
       </c>
       <c r="E11" t="n">
-        <v>10.05222507607344</v>
+        <v>10.67612959468029</v>
       </c>
       <c r="F11" t="n">
-        <v>0.75301525824224</v>
+        <v>0.7471614283011099</v>
       </c>
       <c r="G11" t="n">
-        <v>26.35916777828805</v>
+        <v>28.28533537285564</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63870187914304</v>
+        <v>35.95942016358603</v>
       </c>
       <c r="I11" t="n">
-        <v>3.273705445391743</v>
+        <v>2.394272020416284</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706345364014001</v>
+        <v>4.669758926881936</v>
       </c>
       <c r="K11" t="n">
-        <v>18.51032646833216</v>
+        <v>15.52285473831323</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56175787661434</v>
+        <v>42.98284343367468</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89102241796051</v>
+        <v>99.92026626042779</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.12014607300165</v>
+        <v>82.26985244579757</v>
       </c>
       <c r="C12" t="n">
-        <v>36.9560746963128</v>
+        <v>39.57893911552664</v>
       </c>
       <c r="D12" t="n">
-        <v>1.602272158206713</v>
+        <v>1.651777576273206</v>
       </c>
       <c r="E12" t="n">
-        <v>9.893399760243225</v>
+        <v>10.43819752638888</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538817276559888</v>
+        <v>0.747765927797963</v>
       </c>
       <c r="G12" t="n">
-        <v>24.74904516645297</v>
+        <v>26.77321987831644</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67855947217548</v>
+        <v>35.98851354364106</v>
       </c>
       <c r="I12" t="n">
-        <v>2.731226990417338</v>
+        <v>1.996840944642737</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711760797849931</v>
+        <v>4.673537048737268</v>
       </c>
       <c r="K12" t="n">
-        <v>20.87985392699836</v>
+        <v>17.73014755420246</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07313511431682</v>
+        <v>42.6244057741482</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90906373762799</v>
+        <v>99.9334924438773</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.66599153039654</v>
+        <v>83.43722900596333</v>
       </c>
       <c r="C13" t="n">
-        <v>34.92378135195621</v>
+        <v>40.56152305416057</v>
       </c>
       <c r="D13" t="n">
-        <v>1.495260902135947</v>
+        <v>1.652985967946063</v>
       </c>
       <c r="E13" t="n">
-        <v>9.612360224123664</v>
+        <v>11.0740631065315</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754628495723157</v>
+        <v>0.748312971257916</v>
       </c>
       <c r="G13" t="n">
-        <v>23.09612596901873</v>
+        <v>27.11583462029699</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71291080326522</v>
+        <v>36.33786992220033</v>
       </c>
       <c r="I13" t="n">
-        <v>2.278277037860092</v>
+        <v>1.831206347368554</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716428098269732</v>
+        <v>4.676956070361974</v>
       </c>
       <c r="K13" t="n">
-        <v>23.33400846960346</v>
+        <v>16.56277099403666</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66634276203986</v>
+        <v>42.81471036279462</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92413258359953</v>
+        <v>99.93900441099186</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.50593171030651</v>
+        <v>81.26791019127437</v>
       </c>
       <c r="C14" t="n">
-        <v>39.04426745733036</v>
+        <v>38.67621206625581</v>
       </c>
       <c r="D14" t="n">
-        <v>1.497141438280571</v>
+        <v>1.563965027751387</v>
       </c>
       <c r="E14" t="n">
-        <v>11.93252067623441</v>
+        <v>10.73216709194417</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555775649858816</v>
+        <v>0.7487816452805282</v>
       </c>
       <c r="G14" t="n">
-        <v>24.90813235622716</v>
+        <v>25.65552150278059</v>
       </c>
       <c r="H14" t="n">
-        <v>36.5395272051767</v>
+        <v>36.36062860249017</v>
       </c>
       <c r="I14" t="n">
-        <v>3.150672688240032</v>
+        <v>1.526961038024221</v>
       </c>
       <c r="J14" t="n">
-        <v>4.72235978116176</v>
+        <v>4.6798852830033</v>
       </c>
       <c r="K14" t="n">
-        <v>16.49406828969347</v>
+        <v>18.73208980872563</v>
       </c>
       <c r="L14" t="n">
-        <v>44.35677374707171</v>
+        <v>42.5408312820361</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89510949409555</v>
+        <v>99.94913315701754</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.70915509101687</v>
+        <v>80.31248314297841</v>
       </c>
       <c r="C15" t="n">
-        <v>38.73418884536058</v>
+        <v>37.92161341519253</v>
       </c>
       <c r="D15" t="n">
-        <v>1.467579179208668</v>
+        <v>1.523721298401</v>
       </c>
       <c r="E15" t="n">
-        <v>12.13496043915335</v>
+        <v>10.67392599284461</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563779262274752</v>
+        <v>0.7491879896876847</v>
       </c>
       <c r="G15" t="n">
-        <v>24.41630129545731</v>
+        <v>24.99535721177634</v>
       </c>
       <c r="H15" t="n">
-        <v>36.57823245890102</v>
+        <v>36.38036057397537</v>
       </c>
       <c r="I15" t="n">
-        <v>2.628341753147331</v>
+        <v>1.307505140745377</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72736203892172</v>
+        <v>4.682424935548028</v>
       </c>
       <c r="K15" t="n">
-        <v>17.29084490898314</v>
+        <v>19.68751685702158</v>
       </c>
       <c r="L15" t="n">
-        <v>43.88744755987182</v>
+        <v>42.34730986190548</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91248131421554</v>
+        <v>99.95644013411959</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.18861603513361</v>
+        <v>77.82836692692271</v>
       </c>
       <c r="C16" t="n">
-        <v>36.61972724987844</v>
+        <v>35.63967421286858</v>
       </c>
       <c r="D16" t="n">
-        <v>1.371531670753833</v>
+        <v>1.422616021153811</v>
       </c>
       <c r="E16" t="n">
-        <v>11.70615329404371</v>
+        <v>10.14734910734979</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570672147619066</v>
+        <v>0.7495377709247565</v>
       </c>
       <c r="G16" t="n">
-        <v>22.81834669216581</v>
+        <v>23.33681078111269</v>
       </c>
       <c r="H16" t="n">
-        <v>36.61156626647185</v>
+        <v>36.3973458536406</v>
       </c>
       <c r="I16" t="n">
-        <v>2.192280804674585</v>
+        <v>1.09009632446134</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731670092261917</v>
+        <v>4.684611068279726</v>
       </c>
       <c r="K16" t="n">
-        <v>19.8113839648664</v>
+        <v>22.17163307307728</v>
       </c>
       <c r="L16" t="n">
-        <v>43.49587929211218</v>
+        <v>42.15237312681121</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92699050685702</v>
+        <v>99.96368041275707</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.81302560405742</v>
+        <v>83.13522377718293</v>
       </c>
       <c r="C17" t="n">
-        <v>37.78754309934295</v>
+        <v>39.19356061254135</v>
       </c>
       <c r="D17" t="n">
-        <v>1.372776896105104</v>
+        <v>1.423271434835911</v>
       </c>
       <c r="E17" t="n">
-        <v>12.47021537722866</v>
+        <v>12.0172154928296</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757754562570594</v>
+        <v>0.7498830906055487</v>
       </c>
       <c r="G17" t="n">
-        <v>23.22110389747499</v>
+        <v>25.02124746660527</v>
       </c>
       <c r="H17" t="n">
-        <v>37.02684645397373</v>
+        <v>38.08779966058746</v>
       </c>
       <c r="I17" t="n">
-        <v>2.228362400638114</v>
+        <v>1.149037315434454</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735966016066213</v>
+        <v>4.686769316284678</v>
       </c>
       <c r="K17" t="n">
-        <v>18.18697439594259</v>
+        <v>16.86477622281707</v>
       </c>
       <c r="L17" t="n">
-        <v>43.95127113516459</v>
+        <v>43.90337955844085</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92578863045013</v>
+        <v>99.96171639379928</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.41717832409051</v>
+        <v>84.89522252154028</v>
       </c>
       <c r="C18" t="n">
-        <v>35.73549823127889</v>
+        <v>39.94105504720811</v>
       </c>
       <c r="D18" t="n">
-        <v>1.285041285502804</v>
+        <v>1.424451155310315</v>
       </c>
       <c r="E18" t="n">
-        <v>11.98296703008406</v>
+        <v>12.63115094675281</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583456286770617</v>
+        <v>0.7505046533052165</v>
       </c>
       <c r="G18" t="n">
-        <v>21.73701880317833</v>
+        <v>25.16805461242992</v>
       </c>
       <c r="H18" t="n">
-        <v>37.05572825165513</v>
+        <v>38.11936985583259</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8584171457615</v>
+        <v>2.111037214751817</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739660179231636</v>
+        <v>4.690654083157601</v>
       </c>
       <c r="K18" t="n">
-        <v>20.58282167590946</v>
+        <v>15.10477747845973</v>
       </c>
       <c r="L18" t="n">
-        <v>43.61978113723838</v>
+        <v>44.88385784538183</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93810104442673</v>
+        <v>99.92969037104966</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.4225010025788</v>
+        <v>82.09058531500207</v>
       </c>
       <c r="C19" t="n">
-        <v>35.02680891839739</v>
+        <v>37.46272377442004</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2493488907396</v>
+        <v>1.323543053583607</v>
       </c>
       <c r="E19" t="n">
-        <v>11.90842015323551</v>
+        <v>12.02976957903221</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588451490166331</v>
+        <v>0.7510411459434718</v>
       </c>
       <c r="G19" t="n">
-        <v>21.13326679547948</v>
+        <v>23.38514994376042</v>
       </c>
       <c r="H19" t="n">
-        <v>37.08013676574075</v>
+        <v>38.14661920227238</v>
       </c>
       <c r="I19" t="n">
-        <v>1.549701067012854</v>
+        <v>1.760455228263295</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742782181353958</v>
+        <v>4.694007162146696</v>
       </c>
       <c r="K19" t="n">
-        <v>21.5774989974212</v>
+        <v>17.90941468499793</v>
       </c>
       <c r="L19" t="n">
-        <v>43.34406938568802</v>
+        <v>44.56922161795005</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94837730150661</v>
+        <v>99.94136007736802</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.83536018243942</v>
+        <v>79.25229379716227</v>
       </c>
       <c r="C20" t="n">
-        <v>32.6779764276392</v>
+        <v>34.89571987507205</v>
       </c>
       <c r="D20" t="n">
-        <v>1.155745858674206</v>
+        <v>1.222044561809495</v>
       </c>
       <c r="E20" t="n">
-        <v>11.231582538352</v>
+        <v>11.35190176737805</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592761452086018</v>
+        <v>0.7515048516405802</v>
       </c>
       <c r="G20" t="n">
-        <v>19.54993177660197</v>
+        <v>21.59181391077189</v>
       </c>
       <c r="H20" t="n">
-        <v>37.10119692243335</v>
+        <v>38.17017157985523</v>
       </c>
       <c r="I20" t="n">
-        <v>1.29215103361554</v>
+        <v>1.467951802953403</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745475907553761</v>
+        <v>4.696905322753624</v>
       </c>
       <c r="K20" t="n">
-        <v>24.16463981756057</v>
+        <v>20.74770620283771</v>
       </c>
       <c r="L20" t="n">
-        <v>43.11433650293876</v>
+        <v>44.30767238797182</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95695274813853</v>
+        <v>99.95109846588159</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.64417481640399</v>
+        <v>76.26756479175705</v>
       </c>
       <c r="C21" t="n">
-        <v>36.21139984451894</v>
+        <v>32.13641828104942</v>
       </c>
       <c r="D21" t="n">
-        <v>1.156654869712328</v>
+        <v>1.115883062585494</v>
       </c>
       <c r="E21" t="n">
-        <v>13.15976619803891</v>
+        <v>10.56973020658775</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598733270127134</v>
+        <v>0.7519068584990809</v>
       </c>
       <c r="G21" t="n">
-        <v>21.16358624587248</v>
+        <v>19.71608907440498</v>
       </c>
       <c r="H21" t="n">
-        <v>38.72865571869394</v>
+        <v>38.19059017160716</v>
       </c>
       <c r="I21" t="n">
-        <v>1.926430163244173</v>
+        <v>1.223947552453336</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749208293829458</v>
+        <v>4.699417865619253</v>
       </c>
       <c r="K21" t="n">
-        <v>18.355825183596</v>
+        <v>23.73243520824295</v>
       </c>
       <c r="L21" t="n">
-        <v>45.36861109893569</v>
+        <v>44.09037007173669</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93583612705062</v>
+        <v>99.95922356102905</v>
       </c>
     </row>
   </sheetData>
